--- a/src/test/resources/LoginData.xlsx
+++ b/src/test/resources/LoginData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2492220\IdeaProjects\Testing_CineBook\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA60760B-25BF-4458-B3CA-F7695327E821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27BD545F-68D1-4C19-ABB9-6B8A03B91DA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LoginData" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="38">
   <si>
     <t>role</t>
   </si>
@@ -121,6 +121,21 @@
   </si>
   <si>
     <t>LoinKing</t>
+  </si>
+  <si>
+    <t>admin1</t>
+  </si>
+  <si>
+    <t>tadmin</t>
+  </si>
+  <si>
+    <t>tadmin123</t>
+  </si>
+  <si>
+    <t>User data feeded account</t>
+  </si>
+  <si>
+    <t>Admin data feeded account</t>
   </si>
 </sst>
 </file>
@@ -981,7 +996,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -1024,6 +1039,34 @@
       </c>
       <c r="D3" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4">
+        <v>123</v>
+      </c>
+      <c r="D4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
